--- a/docs/downloads/经营分_河南省区__郑州南片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__郑州南片区_2026-10-18.xlsx
@@ -1563,17 +1563,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7365011208875739188</t>
+          <t>6906608159830312967</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0许昌禹州胖东来药城路店）</t>
+          <t>维也纳3好酒店（许昌襄城迎宾路店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(禹州胖东来店)</t>
+          <t>维也纳3好酒店(襄城迎宾路店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1585,11 +1585,11 @@
         <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1599,13 +1599,13 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1646,27 +1646,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>许昌市</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6713787651494807556</t>
+          <t>7365011208875739188</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>麗枫酒店（郑州新郑轩辕湖店）</t>
+          <t>维也纳国际酒店（5.0许昌禹州胖东来药城路店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>麗枫酒店(郑州新郑轩辕湖店)</t>
+          <t>维也纳国际酒店(禹州胖东来店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1687,19 +1687,19 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1734,31 +1734,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>漯河市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6601138711419684868</t>
+          <t>6713787651494807556</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7天优品（漯河森林公园河上街古镇店）</t>
+          <t>麗枫酒店（郑州新郑轩辕湖店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7天优品(漯河森林公园河上街古镇店)</t>
+          <t>麗枫酒店(郑州新郑轩辕湖店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
@@ -1787,7 +1787,7 @@
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1822,38 +1822,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>漯河市</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7538249229685393454</t>
+          <t>6601138711419684868</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7天酒店（新7天新郑岗李店）</t>
+          <t>7天优品（漯河森林公园河上街古镇店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7天酒店(新7天新郑岗李店)</t>
+          <t>7天优品(漯河森林公园河上街古镇店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>95</v>
       </c>
       <c r="I15" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1869,13 +1869,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6977189256259176455</t>
+          <t>7538249229685393454</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IU酒店（郑州二七万达王胡砦地铁站店）</t>
+          <t>7天酒店（新7天新郑岗李店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IU酒店(郑州二七万达王胡砦地铁站店)</t>
+          <t>7天酒店(新7天新郑岗李店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1937,11 +1937,11 @@
         <v>95</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1951,19 +1951,19 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -1998,22 +1998,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>许昌市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7435888289552271414</t>
+          <t>6977189256259176455</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(许昌东站芙蓉湖旗舰店)</t>
+          <t>IU酒店（郑州二七万达王胡砦地铁站店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(许昌东站芙蓉湖店)</t>
+          <t>IU酒店(郑州二七万达王胡砦地铁站店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <v>95</v>
       </c>
       <c r="I17" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2045,13 +2045,13 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2086,22 +2086,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>许昌市</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7512833267054151714</t>
+          <t>7435888289552271414</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(郑州航空港比亚迪百汇新天地店)</t>
+          <t>维也纳国际酒店(许昌东站芙蓉湖旗舰店)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(郑州航空港比亚迪百汇新天地店)</t>
+          <t>维也纳国际酒店(许昌东站芙蓉湖店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2113,7 +2113,7 @@
         <v>95</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2174,38 +2174,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>漯河市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7273431835986626560</t>
+          <t>7512833267054151714</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（漯河高铁西站万达广场店）</t>
+          <t>维也纳国际酒店(郑州航空港比亚迪百汇新天地店)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(漯河高铁西站店)</t>
+          <t>维也纳国际酒店(郑州航空港比亚迪百汇新天地店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>95</v>
       </c>
       <c r="I19" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2215,13 +2215,13 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
@@ -2262,38 +2262,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>许昌市</t>
+          <t>漯河市</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7589171162707167278</t>
+          <t>7273431835986626560</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>锦江之星(许昌经济技术开发区双龙湖店)</t>
+          <t>维也纳国际酒店（漯河高铁西站万达广场店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>锦江之星酒店(许昌开发区店)</t>
+          <t>维也纳国际酒店(漯河高铁西站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2303,7 +2303,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2315,7 +2315,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2350,34 +2350,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>漯河市</t>
+          <t>许昌市</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7134131616952190984</t>
+          <t>7589171162707167278</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>锦江之星风尚（漯河五一路酒店）</t>
+          <t>锦江之星(许昌经济技术开发区双龙湖店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>锦江之星酒店(漯河五一路店)</t>
+          <t>锦江之星酒店(许昌开发区店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
@@ -2403,7 +2403,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2438,22 +2438,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>漯河市</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6942604771240970243</t>
+          <t>7134131616952190984</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>麗枫酒店（登封嵩山少林文旅服务中心店）</t>
+          <t>锦江之星风尚（漯河五一路酒店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>丽枫酒店(登封嵩山少林文旅服务中心店)</t>
+          <t>锦江之星酒店(漯河五一路店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2465,11 +2465,11 @@
         <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2479,19 +2479,19 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
+        <v>20</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q22" t="n">
         <v>25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>10</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6888633312391235596</t>
+          <t>6942604771240970243</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳酒店（郑州紫荆山南路龙湖店）</t>
+          <t>麗枫酒店（登封嵩山少林文旅服务中心店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳酒店(郑州紫荆山南路龙湖店)</t>
+          <t>丽枫酒店(登封嵩山少林文旅服务中心店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2550,36 +2550,36 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="n">
+        <v>30</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
         <v>25</v>
       </c>
-      <c r="N23" t="n">
-        <v>30</v>
-      </c>
-      <c r="O23" t="n">
-        <v>30</v>
-      </c>
       <c r="P23" t="n">
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2619,17 +2619,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6685481239710943236</t>
+          <t>6888633312391235596</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>希岸酒店（郑州只有河南电影小镇店）</t>
+          <t>维也纳酒店（郑州紫荆山南路龙湖店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>希岸酒店(郑州只有河南电影小镇店)</t>
+          <t>维也纳酒店(郑州紫荆山南路龙湖店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2638,24 +2638,24 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,稳房源,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2702,22 +2702,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>许昌市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6906608159830312967</t>
+          <t>6685481239710943236</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（许昌襄城迎宾路店）</t>
+          <t>希岸酒店（郑州只有河南电影小镇店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(襄城迎宾路店)</t>
+          <t>希岸酒店(郑州只有河南电影小镇店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2749,13 +2749,13 @@
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3142,22 +3142,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>许昌市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7498549963379443724</t>
+          <t>6601139017805203459</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0许昌东站芙蓉湖地铁站店）</t>
+          <t>维也纳酒店（郑州机场店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳酒店(许昌东站芙蓉湖地铁站店)</t>
+          <t>维也纳酒店(郑州机场店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3169,11 +3169,11 @@
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3183,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
@@ -3195,7 +3195,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3235,33 +3235,33 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6601139017805203459</t>
+          <t>6825072419611346951</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳酒店（郑州机场店）</t>
+          <t>锦江之星品尚(新郑龙湖阳光大道店)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳酒店(郑州机场店)</t>
+          <t>锦江之星品尚(新郑龙湖阳光大道店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3271,19 +3271,19 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6825072419611346951</t>
+          <t>6772138950439012363</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>锦江之星品尚(新郑龙湖阳光大道店)</t>
+          <t>麗枫酒店(郑州航海路齐礼阎地铁站店)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>锦江之星品尚(新郑龙湖阳光大道店)</t>
+          <t>麗枫酒店(郑州航海路齐礼阎地铁站店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3345,11 +3345,11 @@
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3359,13 +3359,13 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3411,17 +3411,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6772138950439012363</t>
+          <t>6831736401256646656</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>麗枫酒店(郑州航海路齐礼阎地铁站店)</t>
+          <t>凯里亚德酒店（郑州只有河南海昌公园店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>麗枫酒店(郑州航海路齐礼阎地铁站店)</t>
+          <t>凯里亚德酒店(郑州只有河南海昌公园店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3430,14 +3430,14 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3447,13 +3447,13 @@
         <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
@@ -3494,27 +3494,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>漯河市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6831736401256646656</t>
+          <t>7019683014498060325</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（郑州只有河南海昌公园店）</t>
+          <t>维也纳国际酒店（漯河黄河广场国际会展中心店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(郑州只有河南海昌公园店)</t>
+          <t>维也纳国际酒店(漯河会展中心店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3541,13 +3541,13 @@
         <v>30</v>
       </c>
       <c r="O34" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7019683014498060325</t>
+          <t>7202148845126420513</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（漯河黄河广场国际会展中心店）</t>
+          <t>维也纳酒店（5.0 漯河黄河东路店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(漯河会展中心店)</t>
+          <t>维也纳酒店(5.0 漯河黄河东路店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3629,13 +3629,13 @@
         <v>30</v>
       </c>
       <c r="O35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
@@ -3670,22 +3670,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>漯河市</t>
+          <t>许昌市</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7202148845126420513</t>
+          <t>7498549963379443724</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0 漯河黄河东路店）</t>
+          <t>维也纳酒店（5.0许昌东站芙蓉湖地铁站店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0 漯河黄河东路店)</t>
+          <t>维也纳酒店(许昌东站芙蓉湖地铁站店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3697,11 +3697,11 @@
         <v>105</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3717,13 +3717,13 @@
         <v>30</v>
       </c>
       <c r="O36" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P36" t="n">
         <v>30</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R36" t="n">
         <v>30</v>
@@ -4137,7 +4137,7 @@
         <v>110</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H47" t="n">
